--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92571652975</v>
+        <v>46157.93109542418</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93109542418</v>
+        <v>46157.93178412237</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93178412237</v>
+        <v>46157.93403245353</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93403245353</v>
+        <v>46157.93721210397</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93721210397</v>
+        <v>46158.28219238853</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28219238853</v>
+        <v>46158.29693874134</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29693874134</v>
+        <v>46158.29818597889</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29818597889</v>
+        <v>46158.33390280154</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33390280154</v>
+        <v>46158.36860064494</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/35. Энерго-газ-Ноябрьск (ХВС и водоотведение)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36860064494</v>
+        <v>46158.37290720201</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
